--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:12</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:08</t>
+    <t xml:space="preserve">2026-10-05 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -611,7 +611,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1058718.12</v>
+        <v>1058718.13</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1047318.12</v>
+        <v>1047318.13</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>994706.12</v>
+        <v>994706.13</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>955458.12</v>
+        <v>955458.13</v>
       </c>
     </row>
     <row r="11">
@@ -747,7 +747,7 @@
         <v>2024</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>933417.62</v>
+        <v>933417.63</v>
       </c>
     </row>
     <row r="13">
@@ -815,7 +815,7 @@
         <v>2024</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>911340.12</v>
+        <v>911340.13</v>
       </c>
     </row>
     <row r="17">
@@ -900,7 +900,7 @@
         <v>2024</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>887346.12</v>
+        <v>887346.13</v>
       </c>
     </row>
     <row r="22">
@@ -934,7 +934,7 @@
         <v>2024</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>874265.12</v>
+        <v>874265.13</v>
       </c>
     </row>
     <row r="24">
